--- a/red_book/excel/笔记列表明细表-20260923.xlsx
+++ b/red_book/excel/笔记列表明细表-20260923.xlsx
@@ -361,7 +361,7 @@
         <v>66593.0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4769.0</v>
+        <v>4771.0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.069</v>
@@ -690,13 +690,13 @@
         <v>39012.0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6626.0</v>
+        <v>6630.0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0.171</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>29.0</v>
@@ -831,7 +831,7 @@
         <v>31218.0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3269.0</v>
+        <v>3270.0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0.105</v>
